--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.331494804989</v>
+        <v>2.816367905810712</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6627998277948</v>
+        <v>2.707704972016654</v>
       </c>
       <c r="E2" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F2" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.43072217697984</v>
+        <v>4.457492353759225</v>
       </c>
       <c r="D3" t="n">
-        <v>27.16994540916008</v>
+        <v>4.415116128988513</v>
       </c>
       <c r="E3" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.00635105255333</v>
+        <v>5.201032046039917</v>
       </c>
       <c r="D4" t="n">
-        <v>32.46395620194707</v>
+        <v>5.275392882816399</v>
       </c>
       <c r="E4" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F4" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.72994884011465</v>
+        <v>5.156116686518631</v>
       </c>
       <c r="D5" t="n">
-        <v>31.77925022694605</v>
+        <v>5.164128161878733</v>
       </c>
       <c r="E5" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F5" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.17062682570974</v>
+        <v>5.065226859177832</v>
       </c>
       <c r="D6" t="n">
-        <v>25.03650483598164</v>
+        <v>4.068432035847017</v>
       </c>
       <c r="E6" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F6" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.6324624201849</v>
+        <v>3.677775143280047</v>
       </c>
       <c r="D7" t="n">
-        <v>22.10343000297074</v>
+        <v>3.591807375482745</v>
       </c>
       <c r="E7" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F7" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.78113538844736</v>
+        <v>3.701934500622696</v>
       </c>
       <c r="D8" t="n">
-        <v>23.5539974340548</v>
+        <v>3.827524583033905</v>
       </c>
       <c r="E8" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F8" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.22328612654103</v>
+        <v>5.398783995562917</v>
       </c>
       <c r="D9" t="n">
-        <v>8.31959234468388</v>
+        <v>1.35193375601113</v>
       </c>
       <c r="E9" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F9" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.59989098436467</v>
+        <v>6.109982284959259</v>
       </c>
       <c r="D10" t="n">
-        <v>17.67415834465616</v>
+        <v>2.872050731006627</v>
       </c>
       <c r="E10" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F10" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.48247901493002</v>
+        <v>7.390902839926128</v>
       </c>
       <c r="D11" t="n">
-        <v>44.90648132944483</v>
+        <v>7.297303216034785</v>
       </c>
       <c r="E11" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F11" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.64155387892547</v>
+        <v>8.554252505325389</v>
       </c>
       <c r="D12" t="n">
-        <v>52.10038141903194</v>
+        <v>8.466311980592691</v>
       </c>
       <c r="E12" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F12" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75163725659957</v>
+        <v>4.184641054197431</v>
       </c>
       <c r="D13" t="n">
-        <v>25.48409531693597</v>
+        <v>4.141165489002095</v>
       </c>
       <c r="E13" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F13" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.78359565024867</v>
+        <v>9.552334293165408</v>
       </c>
       <c r="D14" t="n">
-        <v>58.21287080866993</v>
+        <v>9.459591506408863</v>
       </c>
       <c r="E14" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F14" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.71516060864937</v>
+        <v>5.316213598905523</v>
       </c>
       <c r="D15" t="n">
-        <v>32.44752416708478</v>
+        <v>5.272722677151277</v>
       </c>
       <c r="E15" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.54699189686625</v>
+        <v>5.613886183240766</v>
       </c>
       <c r="D16" t="n">
-        <v>33.83568479456262</v>
+        <v>5.498298779116426</v>
       </c>
       <c r="E16" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F16" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.57972000642246</v>
+        <v>6.431704501043649</v>
       </c>
       <c r="D17" t="n">
-        <v>38.9456252091508</v>
+        <v>6.328664096487006</v>
       </c>
       <c r="E17" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F17" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>40.76758910051758</v>
+        <v>6.624733228834107</v>
       </c>
       <c r="D18" t="n">
-        <v>40.39785163474437</v>
+        <v>6.56465089064596</v>
       </c>
       <c r="E18" t="n">
-        <v>10.41306748236414</v>
+        <v>1.692123465884172</v>
       </c>
       <c r="F18" t="n">
-        <v>12.49775044889352</v>
+        <v>2.030884447945197</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
